--- a/Auditoria/Auditoria-modelo.xlsx
+++ b/Auditoria/Auditoria-modelo.xlsx
@@ -920,7 +920,7 @@
     <t xml:space="preserve">Atender pedido de delivery</t>
   </si>
   <si>
-    <t xml:space="preserve">Atendente do turno do almoço (auditor líder) e pizzaiolo do turno do almoço</t>
+    <t xml:space="preserve">Atendente do turno da tarde (auditor líder) e pizzaiolo do turno da tarde</t>
   </si>
   <si>
     <t xml:space="preserve">Líder da expedição e atendentes da noite</t>
@@ -1132,7 +1132,7 @@
     <t xml:space="preserve">A equipe foi treinada em julho. 1 de 2 entregadores admitidos em setembro ainda não recebeu o treinamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">A instrução pode definir quando e como treinar quem entra na equipe depois do treinamento inicial.</t>
+    <t xml:space="preserve">Entregadores admitidos depois do treinamento inicial trabalham sem o treinamento no método exigido pela instrução.</t>
   </si>
   <si>
     <t xml:space="preserve">Líder da expedição
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">Conclusão da auditoria</t>
   </si>
   <si>
-    <t xml:space="preserve">Os padrões da expedição estão implantados e são seguidos. O registro do pedido por telefone e o controle de temperatura precisam de ação corretiva.</t>
+    <t xml:space="preserve">Os padrões da expedição estão implantados e são seguidos. O registro do pedido por telefone, o controle de temperatura e o treinamento de quem entra na expedição precisam de ação corretiva.</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07</t>
@@ -2061,11 +2061,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26498182"/>
-        <c:axId val="15924855"/>
+        <c:axId val="59181089"/>
+        <c:axId val="56120232"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26498182"/>
+        <c:axId val="59181089"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2097,7 +2097,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15924855"/>
+        <c:crossAx val="56120232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2105,7 +2105,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15924855"/>
+        <c:axId val="56120232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2145,7 +2145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26498182"/>
+        <c:crossAx val="59181089"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -6254,7 +6254,7 @@
         <v>292</v>
       </c>
       <c r="G30" s="41" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="H30" s="41" t="n">
         <v>3</v>
@@ -6345,7 +6345,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>301</v>
@@ -6407,7 +6407,7 @@
       <c r="E41" s="27"/>
       <c r="F41" s="23" t="n">
         <f aca="false">COUNTIF(G24:G30,"Não conforme")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6419,7 +6419,7 @@
       <c r="E42" s="27"/>
       <c r="F42" s="23" t="n">
         <f aca="false">COUNTIF(G24:G30,"Oportunidade de melhoria")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Auditoria/Auditoria-modelo.xlsx
+++ b/Auditoria/Auditoria-modelo.xlsx
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">Rotina de temperatura</t>
   </si>
   <si>
-    <t xml:space="preserve">A temperatura da câmara fria é registrada duas vezes por turno?</t>
+    <t xml:space="preserve">A temperatura da câmara fria é registrada em cada turno?</t>
   </si>
   <si>
     <t xml:space="preserve">Registros de 14 dias, 28 turnos</t>
   </si>
   <si>
-    <t xml:space="preserve">3 turnos sem nenhum registro: 12/09 noite, 13/09 noite e 20/09 noite.</t>
+    <t xml:space="preserve">3 turnos sem registro: 12/09 noite, 13/09 noite e 20/09 noite.</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador de entregas</t>
@@ -1113,7 +1113,7 @@
 Em tratamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Rotina de controle: a temperatura da câmara fria deve ser registrada duas vezes por turno.</t>
+    <t xml:space="preserve">Rotina de controle: a temperatura da câmara fria deve ser registrada uma vez em cada turno.</t>
   </si>
   <si>
     <t xml:space="preserve">Planilha de temperatura sem registro nos turnos da noite de 12/09, 13/09 e 20/09, em 28 turnos analisados.</t>
@@ -2061,11 +2061,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="59181089"/>
-        <c:axId val="56120232"/>
+        <c:axId val="60628260"/>
+        <c:axId val="2387560"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59181089"/>
+        <c:axId val="60628260"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2097,7 +2097,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56120232"/>
+        <c:crossAx val="2387560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2105,7 +2105,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56120232"/>
+        <c:axId val="2387560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2145,7 +2145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59181089"/>
+        <c:crossAx val="60628260"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5472,16 +5472,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I7:I21" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="NC maior, NC menor ou Oportunidade de melhoria" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C21" type="list">
       <formula1>"NC maior,NC menor,Oportunidade de melhoria"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Aberta, Em tratamento ou Eficácia verificada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J7:J21" type="list">
       <formula1>"Aberta,Em tratamento,Eficácia verificada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I7:I21" type="date">
+      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
